--- a/protected-files/SmartTec-Mead-DC-Model.xlsx
+++ b/protected-files/SmartTec-Mead-DC-Model.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="167">
   <si>
     <t xml:space="preserve">[ SMARTTEC.DEV · MEAD DATA CENTER · LIVE MODEL — EDIT YELLOW CELLS ON ASSUMPTIONS ]</t>
   </si>
@@ -34,13 +34,13 @@
     <t xml:space="preserve">INVESTOR DASHBOARD</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1A — 8× HGX B200 · 64 GPUs installed, 60 rentable · ~114 kW IT · Mead, Oklahoma</t>
+    <t xml:space="preserve">Phase 1A · V5 — 8× HGX B200 · 64 GPUs, 60 rentable · all-equity, two gated tranches · 8% pref then 80/20</t>
   </si>
   <si>
     <t xml:space="preserve">Total CAPEX</t>
   </si>
   <si>
-    <t xml:space="preserve">Equity required</t>
+    <t xml:space="preserve">Tranche 1 — at close</t>
   </si>
   <si>
     <t xml:space="preserve">Y1 gross revenue</t>
@@ -52,458 +52,488 @@
     <t xml:space="preserve">Y1 operating margin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reserved rate (base)</t>
+    <t xml:space="preserve">Reserved rate (edit on Assumptions)</t>
   </si>
   <si>
     <t xml:space="preserve">Flat payback</t>
   </si>
   <si>
-    <t xml:space="preserve">Equity payback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 DSCR (7-yr term)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 DSCR (5-yr stress)</t>
+    <t xml:space="preserve">Investor Y1 cash yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor 5-yr MOIC (no refi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor IRR (5-yr, no refi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refi DSCR @ underwriting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor promote — Y1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ HOW TO USE ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Edit blue cells on Assumptions and CAPEX. Set the reserved rate to 4.00 to see the underwriting floor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. The base case is ALL EQUITY. The Debt Option tab is an optional stabilisation refinance — illustrative only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Tranche 2 (servers, ~78% of capital) is not callable until the demand gate clears: ≥24 GPUs signed at ≥$4.00/hr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepared July 2026 · V5 structure · Blueprint V4 costs + funded engineering completion · pref/split/gate illustrative pending securities counsel (funded, tranche 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ SMARTTEC.DEV · MEAD DATA CENTER · MODEL INPUTS ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue text on grey = edit these levers. Everything else is a formula. Phase 1A per DC Blueprint V4 (audited 24 Jul 2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ CAPACITY ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved GPUs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billed 24/7/365 regardless of utilisation. Target rate — NOT yet contracted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-demand GPUs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance of the 60 rentable GPUs, sold hourly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7/365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-demand utilisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueprint V4 base case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ RATES — YEAR 1 ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved rate ($/GPU-hr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARGET (workbook default). Documents UNDERWRITE at $4.00 — set this cell to 4.00 to see the floor case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-demand rate ($/GPU-hr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the Jul-2026 independent market median ($6.03 avg / $6.12–6.25 median).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual revenue decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole revenue line declines 10%/yr as newer silicon ships.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ CAPITAL &amp; TERMINAL ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linked live from the CAPEX tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual hardware value @ Y5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliberately zero. The previous edition assumed $450K.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refi LTV (post-stabilisation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional refinance against operating history — NOT in the base case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ ANNUAL OPERATING COSTS ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power &amp; cooling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.4 kW IT full-server draw @ OK ~$0.08/kWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiber — Dobson 100G symmetrical DIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signed quote: $8,075/mo, 60-month term, install waived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team — 3 HPC engineers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$120K avg, Oklahoma market. Raised from 2 when the build doubled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance, property tax, software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate; includes key-man cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ REFI TERMS — ILLUSTRATIVE, NO TERM SHEET ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refi interest rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed for the illustration only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refi term (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typical GPU-collateral tenor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor preferred return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative, on drawn capital. Paid before any sponsor promote.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor share above the pref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance (20%) is the sponsor promote. No fees, no markups.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ SMARTTEC.DEV · MEAD DATA CENTER ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPEX — PHASE 1A BUILD (V5 · GATED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPU servers — 8× HGX B200 8-GPU (64 GPUs, 60 rentable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$375K/system + $20K shipping &amp; install each. Formal quote is a Gate-0 item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfiniBand fabric — 2× QM9790 NDR, optics, NIC spares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch carried at $32,500 vs verified $28,443 reseller floor — conservative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 TB NVMe all-flash storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perishable: NAND +70–75% QoQ in Q2-26. Locks at order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power — 2× Eaton 93PR 100kW UPS (N+1), transformer, PDUs, z1Power LFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPS sized for an earlier smaller build — re-sizing against 114.4 kW is a Gate-0 item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooling + fire suppression — 3× 15-ton CRAC, containment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 tons installed; only 30T with one unit failed, below the 114.4 kW load. Open item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Racks, PDUs, structured cabling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9× 48U racks, switched 3-phase PDUs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management network — switch, firewall, OOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out-of-band management + tenant isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiber cross-connect + termination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobson entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft costs — permitting, legal, PM, AURA dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes $40K AURA monitoring build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering completion &amp; counsel (NEW in V5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4th CRAC $18K · UPS re-size $30K · 64 optics $5.4K · PE review $25K · securities counsel $35K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL CAPEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V5 total: $4,635,121 (V4 $4,504,711 + engineering completion incl. contingency)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ SMARTTEC.DEV · MEAD DATA CENTER · BASE CASE — RATES MODELED FALLING ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIVE-YEAR MODEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved rate ($/GPU-hr) — display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-demand rate ($/GPU-hr) — display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-demand revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net operating income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project cash flow (unlevered)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor distribution (pref + 80/20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ RETURN METRICS — LINKED LIVE ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat payback (Y1 NOI vs total CAPEX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-capital, unlevered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tranche 1 — called at close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything except servers; the only capital at risk pre-gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tranche 2 — servers, post-gate only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not callable until signed demand ≥24 GPUs at ≥$4.00/hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After pref + 80/20 waterfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero residual assumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The floor view — refi and Y6-7 excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor promote — Year 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero until the investor pref is paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ SMARTTEC.DEV · WHERE THE ANCHOR RATE LANDS ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO SENSITIVITY — RATE AND UTILISATION MOVE TOGETHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-demand util</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 NOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refi DSCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue ÷ opex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 1 is the $4.00/65% underwriting basis used for every headline number in the documents; row 3 is the $4.50/75% target the workbook defaults to. All 60 rentable GPUs sold in every row. The reserved rate remains the single most sensitive input and none of it is contracted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ SMARTTEC.DEV · TIERS — 8% PREF, THEN 80/20 · CALLED IN TWO TRANCHES ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTMENT TIERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 levered dist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-yr distributions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pod Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rack Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro-rata of the full raise; distributions are post-waterfall (8% pref, then 80/20). Capital is called ~22% at close (tranche 1) and the balance only if the demand gate clears. IRR shown is the 5-yr no-refi floor view with zero residual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ SMARTTEC.DEV · STABILISATION REFINANCE — OPTIONAL, NOT THE BASE CASE ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REFINANCE ILLUSTRATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refi loan (LTV × CAPEX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80% of CAPEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed — no term sheet signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenders commonly write 3–5 yr on GPU collateral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital remaining after refi distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance of CAPEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual debt service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly amortisation × 12 — matches Blueprint V4 ($57,071/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 DSCR — at workbook rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covenant floors typically sit at 1.25×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 DSCR — at $4.00 underwriting NOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Links to the $4.00 row of the Sensitivity tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity cash flows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-refi equity cash flow (illustration)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 equity cash yield</t>
   </si>
   <si>
     <t xml:space="preserve">Equity MOIC (5-yr)</t>
   </si>
   <si>
-    <t xml:space="preserve">Equity IRR (5-yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ HOW TO USE ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Edit blue cells on Assumptions and CAPEX. Everything else recalculates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Debt Option holds the base-case capital structure — it is not optional in this edition.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. The reserved rate is a TARGET, not a contracted rate. No capacity is under signed contract.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepared July 2026 · Blueprint V4 (audited 24 Jul 2026) · no debt term sheet signed · securities counsel review required before external circulation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ SMARTTEC.DEV · MEAD DATA CENTER · MODEL INPUTS ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMPTIONS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue text on grey = edit these levers. Everything else is a formula. Phase 1A per DC Blueprint V4 (audited 24 Jul 2026).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ CAPACITY ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved GPUs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billed 24/7/365 regardless of utilisation. Target rate — NOT yet contracted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-demand GPUs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance of the 60 rentable GPUs, sold hourly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours per year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/7/365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-demand utilisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint V4 base case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ RATES — YEAR 1 ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved rate ($/GPU-hr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low end of the verified $4.50–$5.50 reserved band. A target, not a signature.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-demand rate ($/GPU-hr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At the Jul-2026 independent market median ($6.03 avg / $6.12–6.25 median).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual revenue decay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whole revenue line declines 10%/yr as newer silicon ships.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ CAPITAL &amp; TERMINAL ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linked live from the CAPEX tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual hardware value @ Y5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deliberately zero. The previous edition assumed $450K.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt share of CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior equipment debt. Balance is equity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ ANNUAL OPERATING COSTS ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power &amp; cooling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.4 kW IT full-server draw @ OK ~$0.08/kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiber — Dobson 100G symmetrical DIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signed quote: $8,075/mo, 60-month term, install waived</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team — 3 HPC engineers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$120K avg, Oklahoma market. Raised from 2 when the build doubled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurance, property tax, software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate; includes key-man cover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ DEBT TERMS ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interest rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumed. NO TERM SHEET SIGNED — confirm before relying on this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Term (years)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPU lenders commonly write 3–5 yr paper. See the 5-yr DSCR on Debt Option.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ SMARTTEC.DEV · MEAD DATA CENTER ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPEX — PHASE 1A BUILD (BLUEPRINT V4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPU servers — 8× HGX B200 8-GPU (64 GPUs, 60 rentable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375K/system + $20K shipping &amp; install each. Formal quote is a Gate-0 item.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfiniBand fabric — 2× QM9790 NDR, optics, NIC spares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch carried at $32,500 vs verified $28,443 reseller floor — conservative.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 TB NVMe all-flash storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perishable: NAND +70–75% QoQ in Q2-26. Locks at order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power — 2× Eaton 93PR 100kW UPS (N+1), transformer, PDUs, z1Power LFP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPS sized for an earlier smaller build — re-sizing against 114.4 kW is a Gate-0 item.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooling + fire suppression — 3× 15-ton CRAC, containment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 tons installed; only 30T with one unit failed, below the 114.4 kW load. Open item.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Racks, PDUs, structured cabling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9× 48U racks, switched 3-phase PDUs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Management network — switch, firewall, OOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Out-of-band management + tenant isolation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiber cross-connect + termination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dobson entry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soft costs — permitting, legal, PM, AURA dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Includes $40K AURA monitoring build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingency %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingency $</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint V4 total: $4,504,711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ SMARTTEC.DEV · MEAD DATA CENTER · BASE CASE — RATES MODELED FALLING ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIVE-YEAR MODEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved rate ($/GPU-hr) — display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-demand rate ($/GPU-hr) — display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-demand revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net operating income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity cash flow (levered)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ RETURN METRICS — LINKED LIVE ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flat payback (Y1 NOI vs total CAPEX)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All-capital basis, before leverage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20% of CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80% LTV — no term sheet signed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levered free cash flow — Year 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOI less annual debt service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity payback (levered)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highly sensitive to the reserved rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity MOIC (5-yr, incl. residual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual assumed $0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levered. Distributions rank behind debt service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ SMARTTEC.DEV · WHERE THE ANCHOR RATE LANDS ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RATE SENSITIVITY — RESERVED RATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 NOI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 DSCR (7-yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue ÷ opex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 60 rentable GPUs sold in every row (48 reserved at the row rate + 12 on-demand at the market rate, 75% utilised). The reserved rate is the single most sensitive input in this model and none of it is contracted yet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ SMARTTEC.DEV · ILLUSTRATIVE PRO-RATA EQUITY ECONOMICS ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INVESTMENT TIERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 levered dist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-yr distributions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pod Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rack Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRR is identical across tiers (pro-rata). Figures are levered — they assume the senior debt on the Debt Option tab and are struck after debt service. Equity distributions rank behind the lender in every period.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ SMARTTEC.DEV · SENIOR DEBT — THIS IS THE BASE CASE ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEBT + EQUITY STRUCTURE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior equipment loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80% of CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumed — no term sheet signed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenders commonly write 3–5 yr on GPU collateral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance of CAPEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual debt service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly amortisation × 12 — matches Blueprint V4 ($57,071/mo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 DSCR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covenant floors typically sit at 1.25×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 DSCR — if 5-yr paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stress case. Materially tighter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity cash flows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOI − debt service (+ residual Y5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1 equity cash yield</t>
-  </si>
-  <si>
     <t xml:space="preserve">Equity IRR</t>
   </si>
   <si>
-    <t xml:space="preserve">Debt secured by hardware; expect the lender to require a sponsor guarantee. Leverage is what produces the equity returns above — and it is why a shortfall in the reserved rate bites harder here than in an all-equity structure. Debt service is fixed; revenue is not.</t>
+    <t xml:space="preserve">Raised against operating history after ~2 billing quarters, when it is cheap — never assumed at close, when it is fiction. Proceeds distribute to investors; the pref then accrues on the reduced base. No term sheet exists; nothing in the plan depends on this closing.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -511,7 +541,6 @@
     <numFmt numFmtId="168" formatCode="0.0&quot; yr&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00\×"/>
     <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -701,7 +730,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -778,7 +807,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -791,10 +824,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -810,10 +839,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -846,6 +871,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -854,11 +887,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -867,6 +904,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -890,7 +931,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1203,14 +1244,14 @@
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">CAPEX!$C$19</f>
-        <v>4504711</v>
+        <v>4635121</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="7" t="n">
         <f aca="false">'5-Year Model'!$C$18</f>
-        <v>900942.2</v>
+        <v>1001121</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1251,14 +1292,14 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">'5-Year Model'!C17</f>
-        <v>2.53356899005067</v>
+        <v>2.60691503422365</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <f aca="false">'5-Year Model'!C21</f>
-        <v>0.824164958465619</v>
+      <c r="F11" s="8" t="n">
+        <f aca="false">'5-Year Model'!C20</f>
+        <v>0.322876131173275</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1266,15 +1307,15 @@
         <v>11</v>
       </c>
       <c r="C12" s="11" t="n">
-        <f aca="false">'Debt Option'!$C$10</f>
-        <v>2.59619450526844</v>
+        <f aca="false">'5-Year Model'!C21</f>
+        <v>1.24190191211837</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <f aca="false">'Debt Option'!$C$11</f>
-        <v>2.00397405483735</v>
+      <c r="F12" s="8" t="n">
+        <f aca="false">'5-Year Model'!C22</f>
+        <v>0.085639669600053</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1282,15 +1323,15 @@
         <v>13</v>
       </c>
       <c r="C13" s="11" t="n">
-        <f aca="false">'5-Year Model'!C22</f>
-        <v>3.67135984283862</v>
+        <f aca="false">'Debt Option'!$C$11</f>
+        <v>2.60186588313566</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="8" t="n">
-        <f aca="false">'5-Year Model'!$C$23</f>
-        <v>0.965502193409051</v>
+      <c r="F13" s="7" t="n">
+        <f aca="false">'5-Year Model'!C23</f>
+        <v>281440.064</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1334,7 +1375,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
@@ -1463,7 +1504,7 @@
       </c>
       <c r="C16" s="18" t="n">
         <f aca="false">CAPEX!$C$19</f>
-        <v>4504711</v>
+        <v>4635121</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>40</v>
@@ -1485,7 +1526,7 @@
         <v>43</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>44</v>
@@ -1540,31 +1581,53 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="20" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="21" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="D25" s="22" t="s">
+      <c r="C25" s="19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="20" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="22" t="s">
+      <c r="C26" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1601,141 +1664,147 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>3160000</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>156440</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="26" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" s="15" t="n">
         <v>120000</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="26" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C9" s="15" t="n">
         <v>227000</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C10" s="15" t="n">
         <v>121000</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" s="15" t="n">
         <v>36500</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="26" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>7700</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>5500</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="26" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>83000</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="12"/>
+      <c r="B15" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>113400</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="29" t="n">
+      <c r="B16" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="28" t="n">
         <f aca="false">SUM(C6:C15)</f>
-        <v>3917140</v>
+        <v>4030540</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>0.15</v>
@@ -1743,23 +1812,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="C18" s="29" t="n">
         <f aca="false">ROUND(C16*C17,0)</f>
-        <v>587571</v>
+        <v>604581</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="32" t="n">
+      <c r="B19" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="31" t="n">
         <f aca="false">C16+C18</f>
-        <v>4504711</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>86</v>
+        <v>4635121</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1798,351 +1867,380 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24"/>
       <c r="C5" s="25" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="33" t="n">
+        <v>101</v>
+      </c>
+      <c r="D6" s="32" t="n">
         <f aca="false">Assumptions!$C$12</f>
         <v>4.5</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="32" t="n">
         <f aca="false">ROUND(D6*(1-Assumptions!$C$14),2)</f>
         <v>4.05</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="32" t="n">
         <f aca="false">ROUND(E6*(1-Assumptions!$C$14),2)</f>
         <v>3.65</v>
       </c>
-      <c r="G6" s="33" t="n">
+      <c r="G6" s="32" t="n">
         <f aca="false">ROUND(F6*(1-Assumptions!$C$14),2)</f>
         <v>3.29</v>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="32" t="n">
         <f aca="false">ROUND(G6*(1-Assumptions!$C$14),2)</f>
         <v>2.96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="33" t="n">
+        <v>102</v>
+      </c>
+      <c r="D7" s="32" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>6.25</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="32" t="n">
         <f aca="false">ROUND(D7*(1-Assumptions!$C$14),2)</f>
         <v>5.63</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="32" t="n">
         <f aca="false">ROUND(E7*(1-Assumptions!$C$14),2)</f>
         <v>5.07</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="32" t="n">
         <f aca="false">ROUND(F7*(1-Assumptions!$C$14),2)</f>
         <v>4.56</v>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="32" t="n">
         <f aca="false">ROUND(G7*(1-Assumptions!$C$14),2)</f>
         <v>4.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="34" t="n">
+        <v>103</v>
+      </c>
+      <c r="D8" s="33" t="n">
         <f aca="false">Assumptions!$C$7*D6*Assumptions!$C$9</f>
         <v>1892160</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="33" t="n">
         <f aca="false">D8*(1-Assumptions!$C$14)</f>
         <v>1702944</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="33" t="n">
         <f aca="false">E8*(1-Assumptions!$C$14)</f>
         <v>1532649.6</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="33" t="n">
         <f aca="false">F8*(1-Assumptions!$C$14)</f>
         <v>1379384.64</v>
       </c>
-      <c r="H8" s="34" t="n">
+      <c r="H8" s="33" t="n">
         <f aca="false">G8*(1-Assumptions!$C$14)</f>
         <v>1241446.176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="34" t="n">
+        <v>104</v>
+      </c>
+      <c r="D9" s="33" t="n">
         <f aca="false">Assumptions!$C$8*D7*Assumptions!$C$9*Assumptions!$C$10</f>
         <v>492750</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E9" s="33" t="n">
         <f aca="false">D9*(1-Assumptions!$C$14)</f>
         <v>443475</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="33" t="n">
         <f aca="false">E9*(1-Assumptions!$C$14)</f>
         <v>399127.5</v>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="33" t="n">
         <f aca="false">F9*(1-Assumptions!$C$14)</f>
         <v>359214.75</v>
       </c>
-      <c r="H9" s="34" t="n">
+      <c r="H9" s="33" t="n">
         <f aca="false">G9*(1-Assumptions!$C$14)</f>
         <v>323293.275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="35" t="n">
+      <c r="B10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="34" t="n">
         <f aca="false">D8+D9</f>
         <v>2384910</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="34" t="n">
         <f aca="false">E8+E9</f>
         <v>2146419</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="34" t="n">
         <f aca="false">F8+F9</f>
         <v>1931777.1</v>
       </c>
-      <c r="G10" s="35" t="n">
+      <c r="G10" s="34" t="n">
         <f aca="false">G8+G9</f>
         <v>1738599.39</v>
       </c>
-      <c r="H10" s="35" t="n">
+      <c r="H10" s="34" t="n">
         <f aca="false">H8+H9</f>
         <v>1564739.451</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="34" t="n">
+        <v>106</v>
+      </c>
+      <c r="D11" s="33" t="n">
         <f aca="false">Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23</f>
         <v>606900</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="33" t="n">
         <f aca="false">Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23</f>
         <v>606900</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="33" t="n">
         <f aca="false">Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23</f>
         <v>606900</v>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="33" t="n">
         <f aca="false">Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23</f>
         <v>606900</v>
       </c>
-      <c r="H11" s="34" t="n">
+      <c r="H11" s="33" t="n">
         <f aca="false">Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23</f>
         <v>606900</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="35" t="n">
+      <c r="B12" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="34" t="n">
         <f aca="false">D10-D11</f>
         <v>1778010</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="34" t="n">
         <f aca="false">E10-E11</f>
         <v>1539519</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <f aca="false">F10-F11</f>
         <v>1324877.1</v>
       </c>
-      <c r="G12" s="35" t="n">
+      <c r="G12" s="34" t="n">
         <f aca="false">G10-G11</f>
         <v>1131699.39</v>
       </c>
-      <c r="H12" s="35" t="n">
+      <c r="H12" s="34" t="n">
         <f aca="false">H10-H11</f>
         <v>957839.451</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="34" t="n">
+        <v>108</v>
+      </c>
+      <c r="D13" s="33" t="n">
         <f aca="false">D12</f>
         <v>1778010</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="33" t="n">
         <f aca="false">D13+E12</f>
         <v>3317529</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="33" t="n">
         <f aca="false">E13+F12</f>
         <v>4642406.1</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="33" t="n">
         <f aca="false">F13+G12</f>
         <v>5774105.49</v>
       </c>
-      <c r="H13" s="34" t="n">
+      <c r="H13" s="33" t="n">
         <f aca="false">G13+H12</f>
         <v>6731944.941</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="34" t="n">
-        <f aca="false">-'Debt Option'!$C$8</f>
-        <v>-900942.2</v>
-      </c>
-      <c r="D14" s="34" t="n">
-        <f aca="false">D12-'Debt Option'!$C$9</f>
-        <v>1093157.61455974</v>
-      </c>
-      <c r="E14" s="34" t="n">
-        <f aca="false">E12-'Debt Option'!$C$9</f>
-        <v>854666.614559736</v>
-      </c>
-      <c r="F14" s="34" t="n">
-        <f aca="false">F12-'Debt Option'!$C$9</f>
-        <v>640024.714559736</v>
-      </c>
-      <c r="G14" s="34" t="n">
-        <f aca="false">G12-'Debt Option'!$C$9</f>
-        <v>446847.004559736</v>
-      </c>
-      <c r="H14" s="34" t="n">
-        <f aca="false">H12-'Debt Option'!$C$9+Assumptions!$C$17</f>
-        <v>272987.065559736</v>
+        <v>109</v>
+      </c>
+      <c r="C14" s="33" t="n">
+        <f aca="false">-CAPEX!$C$19</f>
+        <v>-4635121</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <f aca="false">D12</f>
+        <v>1778010</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <f aca="false">E12</f>
+        <v>1539519</v>
+      </c>
+      <c r="F14" s="33" t="n">
+        <f aca="false">F12</f>
+        <v>1324877.1</v>
+      </c>
+      <c r="G14" s="33" t="n">
+        <f aca="false">G12</f>
+        <v>1131699.39</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <f aca="false">H12+Assumptions!$C$17</f>
+        <v>957839.451</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <f aca="false">-CAPEX!$C$19</f>
+        <v>-4635121</v>
+      </c>
+      <c r="D15" s="36" t="n">
+        <f aca="false">MIN(D12,CAPEX!$C$19*Assumptions!$C$27)+Assumptions!$C$28*MAX(0,D12-CAPEX!$C$19*Assumptions!$C$27)</f>
+        <v>1496569.936</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <f aca="false">MIN(E12,CAPEX!$C$19*Assumptions!$C$27)+Assumptions!$C$28*MAX(0,E12-CAPEX!$C$19*Assumptions!$C$27)</f>
+        <v>1305777.136</v>
+      </c>
+      <c r="F15" s="36" t="n">
+        <f aca="false">MIN(F12,CAPEX!$C$19*Assumptions!$C$27)+Assumptions!$C$28*MAX(0,F12-CAPEX!$C$19*Assumptions!$C$27)</f>
+        <v>1134063.616</v>
+      </c>
+      <c r="G15" s="36" t="n">
+        <f aca="false">MIN(G12,CAPEX!$C$19*Assumptions!$C$27)+Assumptions!$C$28*MAX(0,G12-CAPEX!$C$19*Assumptions!$C$27)</f>
+        <v>979521.448</v>
+      </c>
+      <c r="H15" s="36" t="n">
+        <f aca="false">MIN(H12,CAPEX!$C$19*Assumptions!$C$27)+Assumptions!$C$28*MAX(0,H12-CAPEX!$C$19*Assumptions!$C$27)</f>
+        <v>840433.4968</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="36" t="n">
+        <v>112</v>
+      </c>
+      <c r="C17" s="37" t="n">
         <f aca="false">CAPEX!$C$19/D12</f>
-        <v>2.53356899005067</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>106</v>
+        <v>2.60691503422365</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="37" t="n">
-        <f aca="false">CAPEX!$C$19*(1-Assumptions!$C$18)</f>
-        <v>900942.2</v>
+        <v>114</v>
+      </c>
+      <c r="C18" s="38" t="n">
+        <f aca="false">(CAPEX!$C$16-CAPEX!$C$6)*(1+CAPEX!$C$17)</f>
+        <v>1001121</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="37" t="n">
-        <f aca="false">CAPEX!$C$19*Assumptions!$C$18</f>
-        <v>3603768.8</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>109</v>
+        <v>116</v>
+      </c>
+      <c r="C19" s="38" t="n">
+        <f aca="false">CAPEX!$C$6*(1+CAPEX!$C$17)</f>
+        <v>3634000</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="37" t="n">
-        <f aca="false">D12-'Debt Option'!$C$9</f>
-        <v>1093157.61455974</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>111</v>
+        <v>10</v>
+      </c>
+      <c r="C20" s="39" t="n">
+        <f aca="false">D15/CAPEX!$C$19</f>
+        <v>0.322876131173275</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="36" t="n">
-        <f aca="false">C18/C20</f>
-        <v>0.824164958465619</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>113</v>
+        <v>11</v>
+      </c>
+      <c r="C21" s="40" t="n">
+        <f aca="false">SUM(D15:H15)/CAPEX!$C$19</f>
+        <v>1.24190191211837</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="38" t="n">
-        <f aca="false">SUM(D14:H14)/C18</f>
-        <v>3.67135984283862</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>115</v>
+        <v>12</v>
+      </c>
+      <c r="C22" s="39" t="n">
+        <f aca="false">IRR(C15:H15)</f>
+        <v>0.085639669600053</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="39" t="n">
-        <f aca="false">IRR(C14:H14)</f>
-        <v>0.965502193409051</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>116</v>
+        <v>121</v>
+      </c>
+      <c r="C23" s="38" t="n">
+        <f aca="false">MAX(0,D12-CAPEX!$C$19*Assumptions!$C$27)*(1-Assumptions!$C$28)</f>
+        <v>281440.064</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2259,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
@@ -2180,91 +2278,103 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D5" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="25" t="s">
-        <v>121</v>
-      </c>
       <c r="F5" s="25" t="s">
-        <v>122</v>
+        <v>128</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="34" t="n">
-        <f aca="false">(Assumptions!$C$7*B6*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>1567770</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <f aca="false">CAPEX!$C$19/C6</f>
-        <v>2.87332389317311</v>
-      </c>
-      <c r="E6" s="41" t="n">
-        <f aca="false">C6/'Debt Option'!$C$9</f>
-        <v>2.28920864310364</v>
-      </c>
-      <c r="F6" s="41" t="n">
-        <f aca="false">(Assumptions!$C$7*B6*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>3.58324270884825</v>
+      <c r="C6" s="16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <f aca="false">(Assumptions!$C$7*B6+Assumptions!$C$8*Assumptions!$C$13*C6)*Assumptions!$C$9-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>1502070</v>
+      </c>
+      <c r="E6" s="42" t="n">
+        <f aca="false">CAPEX!$C$19/D6</f>
+        <v>3.08582223198653</v>
+      </c>
+      <c r="F6" s="43" t="n">
+        <f aca="false">D6/'Debt Option'!$C$9</f>
+        <v>2.60186588313566</v>
+      </c>
+      <c r="G6" s="44" t="n">
+        <f aca="false">(Assumptions!$C$7*B6+Assumptions!$C$8*Assumptions!$C$13*C6)*Assumptions!$C$9/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>3.47498764211567</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="17" t="n">
         <v>4.25</v>
       </c>
-      <c r="C7" s="34" t="n">
-        <f aca="false">(Assumptions!$C$7*B7*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>1672890</v>
-      </c>
-      <c r="D7" s="40" t="n">
-        <f aca="false">CAPEX!$C$19/C7</f>
-        <v>2.69277179013563</v>
-      </c>
-      <c r="E7" s="41" t="n">
-        <f aca="false">C7/'Debt Option'!$C$9</f>
-        <v>2.44270157418604</v>
-      </c>
-      <c r="F7" s="41" t="n">
-        <f aca="false">(Assumptions!$C$7*B7*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>3.75645081562037</v>
+      <c r="C7" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <f aca="false">(Assumptions!$C$7*B7+Assumptions!$C$8*Assumptions!$C$13*C7)*Assumptions!$C$9-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>1640040</v>
+      </c>
+      <c r="E7" s="42" t="n">
+        <f aca="false">CAPEX!$C$19/D7</f>
+        <v>2.82622436038145</v>
+      </c>
+      <c r="F7" s="43" t="n">
+        <f aca="false">D7/'Debt Option'!$C$9</f>
+        <v>2.84085570111766</v>
+      </c>
+      <c r="G7" s="44" t="n">
+        <f aca="false">(Assumptions!$C$7*B7+Assumptions!$C$8*Assumptions!$C$13*C7)*Assumptions!$C$9/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>3.70232328225408</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="C8" s="37" t="n">
-        <f aca="false">(Assumptions!$C$7*B8*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+      <c r="C8" s="16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D8" s="38" t="n">
+        <f aca="false">(Assumptions!$C$7*B8+Assumptions!$C$8*Assumptions!$C$13*C8)*Assumptions!$C$9-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
         <v>1778010</v>
       </c>
-      <c r="D8" s="36" t="n">
-        <f aca="false">CAPEX!$C$19/C8</f>
-        <v>2.53356899005067</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <f aca="false">C8/'Debt Option'!$C$9</f>
-        <v>2.59619450526844</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <f aca="false">(Assumptions!$C$7*B8*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+      <c r="E8" s="37" t="n">
+        <f aca="false">CAPEX!$C$19/D8</f>
+        <v>2.60691503422365</v>
+      </c>
+      <c r="F8" s="40" t="n">
+        <f aca="false">D8/'Debt Option'!$C$9</f>
+        <v>3.07984551909967</v>
+      </c>
+      <c r="G8" s="44" t="n">
+        <f aca="false">(Assumptions!$C$7*B8+Assumptions!$C$8*Assumptions!$C$13*C8)*Assumptions!$C$9/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
         <v>3.92965892239249</v>
       </c>
     </row>
@@ -2272,47 +2382,53 @@
       <c r="B9" s="17" t="n">
         <v>4.75</v>
       </c>
-      <c r="C9" s="34" t="n">
-        <f aca="false">(Assumptions!$C$7*B9*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>1883130</v>
-      </c>
-      <c r="D9" s="40" t="n">
-        <f aca="false">CAPEX!$C$19/C9</f>
-        <v>2.39214021336817</v>
-      </c>
-      <c r="E9" s="41" t="n">
-        <f aca="false">C9/'Debt Option'!$C$9</f>
-        <v>2.74968743635084</v>
-      </c>
-      <c r="F9" s="41" t="n">
-        <f aca="false">(Assumptions!$C$7*B9*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>4.10286702916461</v>
+      <c r="C9" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <f aca="false">(Assumptions!$C$7*B9+Assumptions!$C$8*Assumptions!$C$13*C9)*Assumptions!$C$9-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>1915980</v>
+      </c>
+      <c r="E9" s="42" t="n">
+        <f aca="false">CAPEX!$C$19/D9</f>
+        <v>2.41919070136432</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <f aca="false">D9/'Debt Option'!$C$9</f>
+        <v>3.31883533708167</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <f aca="false">(Assumptions!$C$7*B9+Assumptions!$C$8*Assumptions!$C$13*C9)*Assumptions!$C$9/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>4.1569945625309</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="34" t="n">
-        <f aca="false">(Assumptions!$C$7*B10*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>1988250</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <f aca="false">CAPEX!$C$19/C10</f>
-        <v>2.26566628945052</v>
-      </c>
-      <c r="E10" s="41" t="n">
-        <f aca="false">C10/'Debt Option'!$C$9</f>
-        <v>2.90318036743325</v>
-      </c>
-      <c r="F10" s="41" t="n">
-        <f aca="false">(Assumptions!$C$7*B10*Assumptions!$C$9+Assumptions!$C$8*Assumptions!$C$13*Assumptions!$C$9*Assumptions!$C$10)/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
-        <v>4.27607513593673</v>
+      <c r="C10" s="16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <f aca="false">(Assumptions!$C$7*B10+Assumptions!$C$8*Assumptions!$C$13*C10)*Assumptions!$C$9-(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>2053950</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <f aca="false">CAPEX!$C$19/D10</f>
+        <v>2.25668638477081</v>
+      </c>
+      <c r="F10" s="43" t="n">
+        <f aca="false">D10/'Debt Option'!$C$9</f>
+        <v>3.55782515506367</v>
+      </c>
+      <c r="G10" s="44" t="n">
+        <f aca="false">(Assumptions!$C$7*B10+Assumptions!$C$8*Assumptions!$C$13*C10)*Assumptions!$C$9/(Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v>4.3843302026693</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="42" t="s">
-        <v>123</v>
+      <c r="B12" s="45" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2355,153 +2471,152 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>125000</v>
-      </c>
-      <c r="D6" s="43" t="n">
-        <f aca="false">C6/'5-Year Model'!$C$18</f>
-        <v>0.138743639714068</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <f aca="false">D6*'5-Year Model'!$C$20</f>
-        <v>151668.666225166</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <f aca="false">D6*SUM('5-Year Model'!$D$14:$H$14)</f>
-        <v>458919.980354828</v>
-      </c>
-      <c r="G6" s="41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D6" s="46" t="n">
+        <f aca="false">C6/CAPEX!$C$19</f>
+        <v>0.0539360245395967</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <f aca="false">D6*'5-Year Model'!$D$15</f>
+        <v>80719.0327933187</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <f aca="false">D6*SUM('5-Year Model'!$D$15:$H$15)</f>
+        <v>310475.478029592</v>
+      </c>
+      <c r="G6" s="43" t="n">
         <f aca="false">F6/C6</f>
-        <v>3.67135984283862</v>
-      </c>
-      <c r="H6" s="43" t="n">
-        <f aca="false">'5-Year Model'!$C$23</f>
-        <v>0.965502193409051</v>
+        <v>1.24190191211837</v>
+      </c>
+      <c r="H6" s="46" t="n">
+        <f aca="false">'5-Year Model'!$C$22</f>
+        <v>0.085639669600053</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D7" s="43" t="n">
-        <f aca="false">C7/'5-Year Model'!$C$18</f>
-        <v>0.277487279428137</v>
-      </c>
-      <c r="E7" s="34" t="n">
-        <f aca="false">D7*'5-Year Model'!$C$20</f>
-        <v>303337.332450333</v>
-      </c>
-      <c r="F7" s="34" t="n">
-        <f aca="false">D7*SUM('5-Year Model'!$D$14:$H$14)</f>
-        <v>917839.960709655</v>
-      </c>
-      <c r="G7" s="41" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D7" s="46" t="n">
+        <f aca="false">C7/CAPEX!$C$19</f>
+        <v>0.107872049079193</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <f aca="false">D7*'5-Year Model'!$D$15</f>
+        <v>161438.065586637</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <f aca="false">D7*SUM('5-Year Model'!$D$15:$H$15)</f>
+        <v>620950.956059184</v>
+      </c>
+      <c r="G7" s="43" t="n">
         <f aca="false">F7/C7</f>
-        <v>3.67135984283862</v>
-      </c>
-      <c r="H7" s="43" t="n">
-        <f aca="false">'5-Year Model'!$C$23</f>
-        <v>0.965502193409051</v>
+        <v>1.24190191211837</v>
+      </c>
+      <c r="H7" s="46" t="n">
+        <f aca="false">'5-Year Model'!$C$22</f>
+        <v>0.085639669600053</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="26" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D8" s="43" t="n">
-        <f aca="false">C8/'5-Year Model'!$C$18</f>
-        <v>0.499477102970646</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <f aca="false">D8*'5-Year Model'!$C$20</f>
-        <v>546007.198410599</v>
-      </c>
-      <c r="F8" s="34" t="n">
-        <f aca="false">D8*SUM('5-Year Model'!$D$14:$H$14)</f>
-        <v>1652111.92927738</v>
-      </c>
-      <c r="G8" s="41" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <f aca="false">C8/CAPEX!$C$19</f>
+        <v>0.269680122697984</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <f aca="false">D8*'5-Year Model'!$D$15</f>
+        <v>403595.163966593</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <f aca="false">D8*SUM('5-Year Model'!$D$15:$H$15)</f>
+        <v>1552377.39014796</v>
+      </c>
+      <c r="G8" s="43" t="n">
         <f aca="false">F8/C8</f>
-        <v>3.67135984283862</v>
-      </c>
-      <c r="H8" s="43" t="n">
-        <f aca="false">'5-Year Model'!$C$23</f>
-        <v>0.965502193409051</v>
+        <v>1.24190191211837</v>
+      </c>
+      <c r="H8" s="46" t="n">
+        <f aca="false">'5-Year Model'!$C$22</f>
+        <v>0.085639669600053</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="18" t="n">
-        <f aca="false">'5-Year Model'!$C$18</f>
-        <v>900942.2</v>
-      </c>
-      <c r="D9" s="43" t="n">
-        <f aca="false">C9/'5-Year Model'!$C$18</f>
-        <v>1</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <f aca="false">D9*'5-Year Model'!$C$20</f>
-        <v>1093157.61455974</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <f aca="false">D9*SUM('5-Year Model'!$D$14:$H$14)</f>
-        <v>3307683.01379868</v>
-      </c>
-      <c r="G9" s="41" t="n">
+        <v>143</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D9" s="46" t="n">
+        <f aca="false">C9/CAPEX!$C$19</f>
+        <v>0.539360245395967</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <f aca="false">D9*'5-Year Model'!$D$15</f>
+        <v>807190.327933187</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <f aca="false">D9*SUM('5-Year Model'!$D$15:$H$15)</f>
+        <v>3104754.78029592</v>
+      </c>
+      <c r="G9" s="43" t="n">
         <f aca="false">F9/C9</f>
-        <v>3.67135984283862</v>
-      </c>
-      <c r="H9" s="43" t="n">
-        <f aca="false">'5-Year Model'!$C$23</f>
-        <v>0.965502193409051</v>
+        <v>1.24190191211837</v>
+      </c>
+      <c r="H9" s="46" t="n">
+        <f aca="false">'5-Year Model'!$C$22</f>
+        <v>0.085639669600053</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="42" t="s">
-        <v>137</v>
+      <c r="B11" s="45" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2541,180 +2656,180 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="44" t="n">
+        <v>147</v>
+      </c>
+      <c r="C5" s="47" t="n">
         <f aca="false">CAPEX!$C$19*Assumptions!$C$18</f>
-        <v>3603768.8</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>141</v>
+        <v>2317560.5</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="45" t="n">
+        <v>149</v>
+      </c>
+      <c r="C6" s="48" t="n">
         <f aca="false">Assumptions!$C$25</f>
-        <v>0.085</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>142</v>
+        <v>0.09</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="46" t="n">
+        <v>151</v>
+      </c>
+      <c r="C7" s="49" t="n">
         <f aca="false">Assumptions!$C$26</f>
-        <v>7</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>143</v>
+        <v>5</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="34" t="n">
+        <v>153</v>
+      </c>
+      <c r="C8" s="33" t="n">
         <f aca="false">CAPEX!$C$19-C5</f>
-        <v>900942.2</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>145</v>
+        <v>2317560.5</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="34" t="n">
+        <v>155</v>
+      </c>
+      <c r="C9" s="33" t="n">
         <f aca="false">-PMT(C6/12,C7*12,C5)*12</f>
-        <v>684852.385440264</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>147</v>
+        <v>577304.929410799</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="38" t="n">
+        <v>157</v>
+      </c>
+      <c r="C10" s="40" t="n">
         <f aca="false">'5-Year Model'!$D$12/C9</f>
-        <v>2.59619450526844</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="47" t="n">
-        <f aca="false">'5-Year Model'!$D$12/(-PMT(C6/12,60,C5)*12)</f>
-        <v>2.00397405483735</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>151</v>
+        <v>3.07984551909967</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="50" t="n">
+        <f aca="false">Sensitivity!$D$6/C9</f>
+        <v>2.60186588313566</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="48" t="s">
-        <v>152</v>
+      <c r="B12" s="51" t="s">
+        <v>161</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="C13" s="34" t="n">
+        <v>162</v>
+      </c>
+      <c r="C13" s="33" t="n">
         <f aca="false">-C8</f>
-        <v>-900942.2</v>
-      </c>
-      <c r="D13" s="34" t="n">
+        <v>-2317560.5</v>
+      </c>
+      <c r="D13" s="33" t="n">
         <f aca="false">'5-Year Model'!D12-$C$9</f>
-        <v>1093157.61455974</v>
-      </c>
-      <c r="E13" s="34" t="n">
+        <v>1200705.0705892</v>
+      </c>
+      <c r="E13" s="33" t="n">
         <f aca="false">'5-Year Model'!E12-$C$9</f>
-        <v>854666.614559736</v>
-      </c>
-      <c r="F13" s="34" t="n">
+        <v>962214.070589201</v>
+      </c>
+      <c r="F13" s="33" t="n">
         <f aca="false">'5-Year Model'!F12-$C$9</f>
-        <v>640024.714559736</v>
-      </c>
-      <c r="G13" s="34" t="n">
+        <v>747572.170589201</v>
+      </c>
+      <c r="G13" s="33" t="n">
         <f aca="false">'5-Year Model'!G12-$C$9</f>
-        <v>446847.004559736</v>
-      </c>
-      <c r="H13" s="34" t="n">
+        <v>554394.460589201</v>
+      </c>
+      <c r="H13" s="33" t="n">
         <f aca="false">'5-Year Model'!H12-$C$9+Assumptions!$C$17</f>
-        <v>272987.065559736</v>
+        <v>380534.521589201</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C15" s="39" t="n">
         <f aca="false">D13/C8</f>
-        <v>1.21334932980133</v>
+        <v>0.518090065216939</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="38" t="n">
+        <v>164</v>
+      </c>
+      <c r="C16" s="40" t="n">
         <f aca="false">SUM(D13:H13)/C8</f>
-        <v>3.67135984283862</v>
+        <v>1.65925346671468</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">IRR(C13:H13)</f>
-        <v>0.965502193409051</v>
+        <v>0.248298582620645</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="42" t="s">
-        <v>156</v>
+      <c r="B19" s="45" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
